--- a/output/pdf_financials_xlsx/NPR.xlsx
+++ b/output/pdf_financials_xlsx/NPR.xlsx
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.007213</v>
@@ -13822,7 +13822,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>0.0105</v>
       </c>

--- a/output/pdf_financials_xlsx/NPR.xlsx
+++ b/output/pdf_financials_xlsx/NPR.xlsx
@@ -1032,25 +1032,25 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.226686</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.175549</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.033261</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.141842</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.364562</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.16444</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.090974</v>
       </c>
     </row>
     <row r="13">
@@ -1961,25 +1961,25 @@
         <v>-5.87357</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-10.407594</v>
+        <v>-10.180908</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.358578</v>
+        <v>-5.183029</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.567475</v>
+        <v>-1.534214</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.472448</v>
+        <v>-4.330606</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.388882</v>
+        <v>-5.02432</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-4.774625</v>
+        <v>-4.610185</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.20309</v>
+        <v>-5.112116</v>
       </c>
     </row>
     <row r="28">
@@ -2071,25 +2071,25 @@
         <v>-5.87357</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-10.407594</v>
+        <v>-10.180908</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.358578</v>
+        <v>-5.183029</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.567475</v>
+        <v>-1.534214</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.472448</v>
+        <v>-4.330606</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.388882</v>
+        <v>-5.02432</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-4.774625</v>
+        <v>-4.610185</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.20309</v>
+        <v>-5.112116</v>
       </c>
     </row>
     <row r="30">
@@ -2311,46 +2311,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.238268</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.041155</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.008267999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.037053</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.169679</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.884568</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>17.99887</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>10.825749</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.299125</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.115374</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>8.087935999999999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.304713</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.273175</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.218888</v>
       </c>
     </row>
     <row r="35">
@@ -2409,46 +2409,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.238268</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.041155</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.008267999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.037053</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.169679</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.884568</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>17.99887</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>10.825749</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.299125</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.115374</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>8.087935999999999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.304713</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.273175</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.218888</v>
       </c>
     </row>
     <row r="37">
@@ -3024,19 +3024,19 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.330275</v>
+        <v>0.214901</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>8.308097</v>
+        <v>0.220161</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.564952</v>
+        <v>0.260239</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.55697</v>
+        <v>0.283795</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.165152</v>
+        <v>0.946264</v>
       </c>
     </row>
     <row r="49">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/output/pdf_financials_xlsx/NPR.xlsx
+++ b/output/pdf_financials_xlsx/NPR.xlsx
@@ -2025,16 +2025,16 @@
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.051623</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.07446800000000001</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.048257</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.025412</v>
       </c>
     </row>
     <row r="29">
@@ -2080,16 +2080,16 @@
         <v>-1.534214</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.330606</v>
+        <v>-4.278983</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.02432</v>
+        <v>-4.949852</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-4.610185</v>
+        <v>-4.561928</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.112116</v>
+        <v>-5.086704</v>
       </c>
     </row>
     <row r="30">
@@ -5665,16 +5665,16 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.051623</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.07446800000000001</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.048257</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.025412</v>
       </c>
     </row>
     <row r="101">
@@ -14422,7 +14422,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NPR.xlsx
+++ b/output/pdf_financials_xlsx/NPR.xlsx
@@ -5581,10 +5581,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.021495</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.165795</v>
@@ -5632,10 +5630,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -5683,10 +5679,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -5734,10 +5728,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -5785,10 +5777,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -5836,10 +5826,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.021102</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>-0.034507</v>
@@ -5887,10 +5875,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -5938,10 +5924,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.021102</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.034507</v>
@@ -5989,10 +5973,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -6040,10 +6022,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -6091,10 +6071,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -6142,10 +6120,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -6193,10 +6169,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6229,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.210156</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -6244,10 +6218,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -6295,10 +6267,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -6346,10 +6316,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -6397,10 +6365,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -6448,10 +6414,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -6499,10 +6463,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -6550,10 +6512,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -6601,10 +6561,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>0</v>
@@ -6660,10 +6618,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -6711,10 +6667,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -6762,10 +6716,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -6813,10 +6765,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -6864,10 +6814,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -6915,10 +6863,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -6966,10 +6912,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -7094,10 +7038,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -7145,10 +7087,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.240905</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.00626</v>
@@ -7198,10 +7138,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>7e-06</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.238268</v>
@@ -7249,10 +7187,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -7300,10 +7236,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.238268</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.197113</v>
@@ -7351,10 +7285,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.238275</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.041155</v>
@@ -7402,10 +7334,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -7438,7 +7368,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.210156</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -7453,10 +7383,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.002637</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.203373</v>
@@ -7495,7 +7423,7 @@
         <v>-3.09892</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-3.99832</v>
+        <v>-4.208476</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-4.540516</v>
@@ -7515,7 +7443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R217"/>
+  <dimension ref="A1:R226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16224,7 +16152,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -17076,7 +17008,11 @@
           <t>Proceeds received for subsequent private placement</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -18874,7 +18810,11 @@
           <t>Gross proceeds from private placement (note 7)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -19299,28 +19239,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>General and administration (note 12 and 14) $</t>
+          <t>Net loss for the period</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>-0.021495</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -19377,38 +19315,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q141" s="5" t="n">
-        <v>0.937819</v>
-      </c>
-      <c r="R141" s="5" t="n">
-        <v>1.057027</v>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Change in non9cash working capital</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Professional fees (note 14)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amounts receivable and other assets</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>-0.002244</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -19465,34 +19401,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q142" s="5" t="n">
-        <v>0.20895</v>
-      </c>
-      <c r="R142" s="5" t="n">
-        <v>0.243031</v>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Change in non9cash working capital</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Investor relations and marketing</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>0.021102</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -19544,37 +19486,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P143" s="5" t="n">
-        <v>0.106717</v>
-      </c>
-      <c r="Q143" s="5" t="n">
-        <v>0.190504</v>
-      </c>
-      <c r="R143" s="5" t="n">
-        <v>0.616837</v>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Change in non9cash working capital</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Corporate development</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>-0.002637</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -19636,31 +19586,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R144" s="5" t="n">
-        <v>0.08</v>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (note 13)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from issuance of common shares (Note 4) $</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0.3</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -19717,34 +19671,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q145" s="5" t="n">
-        <v>3.065951</v>
-      </c>
-      <c r="R145" s="5" t="n">
-        <v>2.503637</v>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Write-off of exploration property (note 7)</t>
+          <t>Share issuance costs paid</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E146" s="5" t="n">
+        <v>-0.059095</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -19806,31 +19762,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R146" s="5" t="n">
-        <v>0.095</v>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 11 and 14)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash from financing activities</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>0.240905</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -19887,38 +19847,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q147" s="5" t="n">
-        <v>0.535841</v>
-      </c>
-      <c r="R147" s="5" t="n">
-        <v>0.698532</v>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Increase in cash</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>0.238268</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -19970,41 +19932,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P148" s="5" t="n">
-        <v>-0.364562</v>
-      </c>
-      <c r="Q148" s="5" t="n">
-        <v>-0.16444</v>
-      </c>
-      <c r="R148" s="5" t="n">
-        <v>-0.090974</v>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Net Loss</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>7e-06</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -20061,11 +20027,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q149" s="5" t="n">
-        <v>-4.774625</v>
-      </c>
-      <c r="R149" s="5" t="n">
-        <v>-5.20309</v>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -20081,10 +20051,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Currency translation differences</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>General and administration (note 12 and 14) $</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -20145,13 +20119,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q150" s="5" t="n">
+        <v>0.937819</v>
       </c>
       <c r="R150" s="5" t="n">
-        <v>-0.148013</v>
+        <v>1.057027</v>
       </c>
     </row>
     <row r="151">
@@ -20167,10 +20139,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss) $</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Professional fees (note 14)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -20232,10 +20208,10 @@
         </is>
       </c>
       <c r="Q151" s="5" t="n">
-        <v>-4.774625</v>
+        <v>0.20895</v>
       </c>
       <c r="R151" s="5" t="n">
-        <v>-5.351103</v>
+        <v>0.243031</v>
       </c>
     </row>
     <row r="152">
@@ -20251,7 +20227,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share $</t>
+          <t>Investor relations and marketing</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -20311,13 +20287,13 @@
         </is>
       </c>
       <c r="P152" s="5" t="n">
-        <v>-2.1e-07</v>
+        <v>0.106717</v>
       </c>
       <c r="Q152" s="5" t="n">
-        <v>-1.6e-07</v>
+        <v>0.190504</v>
       </c>
       <c r="R152" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>0.616837</v>
       </c>
     </row>
     <row r="153">
@@ -20328,12 +20304,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+          <t>Corporate development</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -20392,14 +20368,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P153" s="5" t="n">
-        <v>25.881296</v>
-      </c>
-      <c r="Q153" s="5" t="n">
-        <v>30.420301</v>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R153" s="5" t="n">
-        <v>39.848812</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="154">
@@ -20415,7 +20395,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Contractor fees $</t>
+          <t>Exploration and evaluation expenses (note 13)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -20474,16 +20454,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P154" s="5" t="n">
-        <v>0.025422</v>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q154" s="5" t="n">
-        <v>0.052939</v>
-      </c>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.065951</v>
+      </c>
+      <c r="R154" s="5" t="n">
+        <v>2.503637</v>
       </c>
     </row>
     <row r="155">
@@ -20499,14 +20479,10 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Write-off of exploration property (note 7)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -20562,16 +20538,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P155" s="5" t="n">
-        <v>0.276819</v>
-      </c>
-      <c r="Q155" s="5" t="n">
-        <v>0.101419</v>
-      </c>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R155" s="5" t="n">
+        <v>0.095</v>
       </c>
     </row>
     <row r="156">
@@ -20587,14 +20565,10 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>General and administration (note 11 and 13)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation (note 11 and 14)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -20650,16 +20624,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P156" s="5" t="n">
-        <v>1.058648</v>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q156" s="5" t="n">
-        <v>0.783462</v>
-      </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.535841</v>
+      </c>
+      <c r="R156" s="5" t="n">
+        <v>0.698532</v>
       </c>
     </row>
     <row r="157">
@@ -20675,12 +20649,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Professional fees (note 13)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -20739,15 +20713,13 @@
         </is>
       </c>
       <c r="P157" s="5" t="n">
-        <v>0.255158</v>
+        <v>-0.364562</v>
       </c>
       <c r="Q157" s="5" t="n">
-        <v>0.20895</v>
-      </c>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.16444</v>
+      </c>
+      <c r="R157" s="5" t="n">
+        <v>-0.090974</v>
       </c>
     </row>
     <row r="158">
@@ -20763,10 +20735,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (note 12)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Net Loss</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -20822,16 +20798,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P158" s="5" t="n">
-        <v>3.110443</v>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q158" s="5" t="n">
-        <v>3.065951</v>
-      </c>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.774625</v>
+      </c>
+      <c r="R158" s="5" t="n">
+        <v>-5.20309</v>
       </c>
     </row>
     <row r="159">
@@ -20847,7 +20823,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 10 and 13)</t>
+          <t>Currency translation differences</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -20906,16 +20882,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P159" s="5" t="n">
-        <v>0.9202360000000001</v>
-      </c>
-      <c r="Q159" s="5" t="n">
-        <v>0.535841</v>
-      </c>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R159" s="5" t="n">
+        <v>-0.148013</v>
       </c>
     </row>
     <row r="160">
@@ -20931,14 +20909,10 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -20994,16 +20968,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P160" s="5" t="n">
-        <v>-5.388882</v>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q160" s="5" t="n">
         <v>-4.774625</v>
       </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R160" s="5" t="n">
+        <v>-5.351103</v>
       </c>
     </row>
     <row r="161">
@@ -21014,12 +20988,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Contractor fees $</t>
+          <t>Basic and diluted net loss per share $</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -21068,24 +21042,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N161" s="5" t="n">
-        <v>0.117007</v>
-      </c>
-      <c r="O161" s="5" t="n">
-        <v>0.025017</v>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P161" s="5" t="n">
-        <v>0.025422</v>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.1e-07</v>
+      </c>
+      <c r="Q161" s="5" t="n">
+        <v>-1.6e-07</v>
+      </c>
+      <c r="R161" s="5" t="n">
+        <v>-1.3e-07</v>
       </c>
     </row>
     <row r="162">
@@ -21096,19 +21070,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -21124,42 +21094,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H162" s="5" t="n">
-        <v>0.021759</v>
-      </c>
-      <c r="I162" s="5" t="n">
-        <v>0.054141</v>
-      </c>
-      <c r="J162" s="5" t="n">
-        <v>0.087645</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>0.356639</v>
-      </c>
-      <c r="L162" s="5" t="n">
-        <v>0.6837530000000001</v>
-      </c>
-      <c r="M162" s="5" t="n">
-        <v>0.271041</v>
-      </c>
-      <c r="N162" s="5" t="n">
-        <v>0.056926</v>
-      </c>
-      <c r="O162" s="5" t="n">
-        <v>0.202991</v>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P162" s="5" t="n">
-        <v>0.276819</v>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.881296</v>
+      </c>
+      <c r="Q162" s="5" t="n">
+        <v>30.420301</v>
+      </c>
+      <c r="R162" s="5" t="n">
+        <v>39.848812</v>
       </c>
     </row>
     <row r="163">
@@ -21170,19 +21152,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Office and general (note 12)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Contractor fees $</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -21228,19 +21206,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N163" s="5" t="n">
-        <v>0.6582209999999999</v>
-      </c>
-      <c r="O163" s="5" t="n">
-        <v>0.767208</v>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P163" s="5" t="n">
-        <v>1.1305</v>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025422</v>
+      </c>
+      <c r="Q163" s="5" t="n">
+        <v>0.052939</v>
       </c>
       <c r="R163" t="inlineStr">
         <is>
@@ -21256,17 +21236,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Professional fees (note 12)</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -21314,19 +21294,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N164" s="5" t="n">
-        <v>0.156188</v>
-      </c>
-      <c r="O164" s="5" t="n">
-        <v>0.180794</v>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.255158</v>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.276819</v>
+      </c>
+      <c r="Q164" s="5" t="n">
+        <v>0.101419</v>
       </c>
       <c r="R164" t="inlineStr">
         <is>
@@ -21342,17 +21324,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General and administration (note 11 and 13)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -21385,28 +21367,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K165" s="5" t="n">
-        <v>0.257633</v>
-      </c>
-      <c r="L165" s="5" t="n">
-        <v>0.486933</v>
-      </c>
-      <c r="M165" s="5" t="n">
-        <v>0.037918</v>
-      </c>
-      <c r="N165" s="5" t="n">
-        <v>0.001015</v>
-      </c>
-      <c r="O165" s="5" t="n">
-        <v>0.001984</v>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P165" s="5" t="n">
-        <v>0.034865</v>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.058648</v>
+      </c>
+      <c r="Q165" s="5" t="n">
+        <v>0.783462</v>
       </c>
       <c r="R165" t="inlineStr">
         <is>
@@ -21422,15 +21412,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (note 13)</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Professional fees (note 13)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -21481,16 +21475,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O166" s="5" t="n">
-        <v>2.097914</v>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P166" s="5" t="n">
-        <v>3.110443</v>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.255158</v>
+      </c>
+      <c r="Q166" s="5" t="n">
+        <v>0.20895</v>
       </c>
       <c r="R166" t="inlineStr">
         <is>
@@ -21506,12 +21500,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Loss on disposition of exploration and evaluation assets</t>
+          <t>Exploration and evaluation expenses (note 12)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -21565,18 +21559,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O167" s="5" t="n">
-        <v>0.67944</v>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P167" s="5" t="n">
+        <v>3.110443</v>
+      </c>
+      <c r="Q167" s="5" t="n">
+        <v>3.065951</v>
       </c>
       <c r="R167" t="inlineStr">
         <is>
@@ -21592,12 +21584,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Stock-based compensation (notes 10 and 12)</t>
+          <t>Share-based compensation (note 10 and 13)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -21646,19 +21638,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N168" s="5" t="n">
-        <v>0.54262</v>
-      </c>
-      <c r="O168" s="5" t="n">
-        <v>0.658942</v>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P168" s="5" t="n">
         <v>0.9202360000000001</v>
       </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q168" s="5" t="n">
+        <v>0.535841</v>
       </c>
       <c r="R168" t="inlineStr">
         <is>
@@ -21674,17 +21668,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -21722,25 +21716,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L169" s="5" t="n">
-        <v>-0.226686</v>
-      </c>
-      <c r="M169" s="5" t="n">
-        <v>-0.175549</v>
-      </c>
-      <c r="N169" s="5" t="n">
-        <v>-0.033261</v>
-      </c>
-      <c r="O169" s="5" t="n">
-        <v>-0.141842</v>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P169" s="5" t="n">
-        <v>-0.364562</v>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.388882</v>
+      </c>
+      <c r="Q169" s="5" t="n">
+        <v>-4.774625</v>
       </c>
       <c r="R169" t="inlineStr">
         <is>
@@ -21761,14 +21761,10 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Contractor fees $</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -21779,11 +21775,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G170" s="5" t="n">
-        <v>-0.026939</v>
-      </c>
-      <c r="H170" s="5" t="n">
-        <v>-0.08699999999999999</v>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -21795,11 +21795,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K170" s="5" t="n">
-        <v>-5.87357</v>
-      </c>
-      <c r="L170" s="5" t="n">
-        <v>-10.407594</v>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -21807,13 +21811,13 @@
         </is>
       </c>
       <c r="N170" s="5" t="n">
-        <v>-1.567475</v>
+        <v>0.117007</v>
       </c>
       <c r="O170" s="5" t="n">
-        <v>-4.472448</v>
+        <v>0.025017</v>
       </c>
       <c r="P170" s="5" t="n">
-        <v>-5.388882</v>
+        <v>0.025422</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -21839,10 +21843,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (note 11) $</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -21853,45 +21861,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G171" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H171" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021759</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>0.054141</v>
+      </c>
+      <c r="J171" s="5" t="n">
+        <v>0.087645</v>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>0.356639</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>0.6837530000000001</v>
+      </c>
+      <c r="M171" s="5" t="n">
+        <v>0.271041</v>
       </c>
       <c r="N171" s="5" t="n">
-        <v>-8e-08</v>
+        <v>0.056926</v>
       </c>
       <c r="O171" s="5" t="n">
-        <v>-1.9e-07</v>
+        <v>0.202991</v>
       </c>
       <c r="P171" s="5" t="n">
-        <v>-2.1e-07</v>
+        <v>0.276819</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -21912,15 +21912,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted (note 11)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Office and general (note 12)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -21931,11 +21935,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G172" s="5" t="n">
-        <v>2.0313</v>
-      </c>
-      <c r="H172" s="5" t="n">
-        <v>2.553682</v>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -21963,13 +21971,13 @@
         </is>
       </c>
       <c r="N172" s="5" t="n">
-        <v>20.051087</v>
+        <v>0.6582209999999999</v>
       </c>
       <c r="O172" s="5" t="n">
-        <v>23.179907</v>
+        <v>0.767208</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>25.881296</v>
+        <v>1.1305</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -21995,10 +22003,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Exploration expenses (note 14)</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Professional fees (note 12)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -22045,15 +22057,13 @@
         </is>
       </c>
       <c r="N173" s="5" t="n">
-        <v>0.218759</v>
+        <v>0.156188</v>
       </c>
       <c r="O173" s="5" t="n">
-        <v>2.097914</v>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.180794</v>
+      </c>
+      <c r="P173" s="5" t="n">
+        <v>0.255158</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -22079,10 +22089,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Loss on disposition of exploration and evaluation assets (note 5)</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -22113,33 +22127,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K174" s="5" t="n">
+        <v>0.257633</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>0.486933</v>
+      </c>
+      <c r="M174" s="5" t="n">
+        <v>0.037918</v>
+      </c>
+      <c r="N174" s="5" t="n">
+        <v>0.001015</v>
       </c>
       <c r="O174" s="5" t="n">
-        <v>0.67944</v>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001984</v>
+      </c>
+      <c r="P174" s="5" t="n">
+        <v>0.034865</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -22165,7 +22169,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Loss from continuing operations for the year</t>
+          <t>Exploration and evaluation expenses (note 13)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -22214,16 +22218,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N175" s="5" t="n">
-        <v>-1.717475</v>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O175" s="5" t="n">
-        <v>-4.472448</v>
-      </c>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.097914</v>
+      </c>
+      <c r="P175" s="5" t="n">
+        <v>3.110443</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
@@ -22249,7 +22253,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Gain from discontinued operations (note 13)</t>
+          <t>Loss on disposition of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -22298,13 +22302,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N176" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O176" s="5" t="n">
+        <v>0.67944</v>
       </c>
       <c r="P176" t="inlineStr">
         <is>
@@ -22335,14 +22339,10 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Salaries and benefits $</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (notes 10 and 12)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -22363,35 +22363,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I177" s="5" t="n">
-        <v>0.262675</v>
-      </c>
-      <c r="J177" s="5" t="n">
-        <v>1.145458</v>
-      </c>
-      <c r="K177" s="5" t="n">
-        <v>2.41073</v>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v>3.718306</v>
-      </c>
-      <c r="M177" s="5" t="n">
-        <v>1.524189</v>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="5" t="n">
+        <v>0.54262</v>
+      </c>
+      <c r="O177" s="5" t="n">
+        <v>0.658942</v>
+      </c>
+      <c r="P177" s="5" t="n">
+        <v>0.9202360000000001</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
@@ -22417,10 +22421,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Contractor fees (note 9)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -22457,25 +22465,19 @@
         </is>
       </c>
       <c r="L178" s="5" t="n">
-        <v>0.973942</v>
+        <v>-0.226686</v>
       </c>
       <c r="M178" s="5" t="n">
-        <v>1.563873</v>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.175549</v>
+      </c>
+      <c r="N178" s="5" t="n">
+        <v>-0.033261</v>
+      </c>
+      <c r="O178" s="5" t="n">
+        <v>-0.141842</v>
+      </c>
+      <c r="P178" s="5" t="n">
+        <v>-0.364562</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -22501,12 +22503,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -22519,45 +22521,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I179" s="5" t="n">
-        <v>0.01881</v>
-      </c>
-      <c r="J179" s="5" t="n">
-        <v>0.266545</v>
+      <c r="G179" s="5" t="n">
+        <v>-0.026939</v>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K179" s="5" t="n">
-        <v>0.787968</v>
+        <v>-5.87357</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>1.408514</v>
-      </c>
-      <c r="M179" s="5" t="n">
-        <v>0.87295</v>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.407594</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="5" t="n">
+        <v>-1.567475</v>
+      </c>
+      <c r="O179" s="5" t="n">
+        <v>-4.472448</v>
+      </c>
+      <c r="P179" s="5" t="n">
+        <v>-5.388882</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -22583,14 +22581,10 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Basic and diluted net loss per share (note 11) $</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -22601,45 +22595,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I180" s="5" t="n">
-        <v>0.165683</v>
-      </c>
-      <c r="J180" s="5" t="n">
-        <v>0.149271</v>
-      </c>
-      <c r="K180" s="5" t="n">
-        <v>0.483479</v>
-      </c>
-      <c r="L180" s="5" t="n">
-        <v>0.4847</v>
-      </c>
-      <c r="M180" s="5" t="n">
-        <v>0.359437</v>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G180" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="O180" s="5" t="n">
+        <v>-1.9e-07</v>
+      </c>
+      <c r="P180" s="5" t="n">
+        <v>-2.1e-07</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -22660,12 +22654,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bad debt expense</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted (note 11)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -22679,51 +22673,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G181" s="5" t="n">
+        <v>2.0313</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>2.553682</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J181" s="5" t="n">
-        <v>0.01725</v>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L181" s="5" t="n">
-        <v>0.08648500000000001</v>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N181" s="5" t="n">
+        <v>20.051087</v>
+      </c>
+      <c r="O181" s="5" t="n">
+        <v>23.179907</v>
+      </c>
+      <c r="P181" s="5" t="n">
+        <v>25.881296</v>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
@@ -22749,7 +22737,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 6)</t>
+          <t>Exploration expenses (note 14)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -22788,21 +22776,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L182" s="5" t="n">
-        <v>2.791647</v>
-      </c>
-      <c r="M182" s="5" t="n">
-        <v>0.9047190000000001</v>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="5" t="n">
+        <v>0.218759</v>
+      </c>
+      <c r="O182" s="5" t="n">
+        <v>2.097914</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -22833,14 +22821,10 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Loss on disposition of exploration and evaluation assets (note 5)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -22851,36 +22835,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G183" s="5" t="n">
-        <v>0.026939</v>
-      </c>
-      <c r="H183" s="5" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="I183" s="5" t="n">
-        <v>3.440042</v>
-      </c>
-      <c r="J183" s="5" t="n">
-        <v>2.348152</v>
-      </c>
-      <c r="K183" s="5" t="n">
-        <v>6.246497</v>
-      </c>
-      <c r="L183" s="5" t="n">
-        <v>10.407594</v>
-      </c>
-      <c r="M183" s="5" t="n">
-        <v>5.358578</v>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O183" s="5" t="n">
+        <v>0.67944</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
@@ -22911,14 +22907,10 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss from continuing operations for the year</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -22954,21 +22946,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L184" s="5" t="n">
-        <v>-10.407594</v>
-      </c>
-      <c r="M184" s="5" t="n">
-        <v>-5.358578</v>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="5" t="n">
+        <v>-1.717475</v>
+      </c>
+      <c r="O184" s="5" t="n">
+        <v>-4.472448</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
@@ -22999,7 +22991,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (note 8) $</t>
+          <t>Gain from discontinued operations (note 13)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -23038,16 +23030,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L185" s="5" t="n">
-        <v>-4.5e-07</v>
-      </c>
-      <c r="M185" s="5" t="n">
-        <v>-2.2e-07</v>
-      </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -23078,15 +23072,19 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted (note 8)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Salaries and benefits $</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -23107,26 +23105,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I186" s="5" t="n">
+        <v>0.262675</v>
+      </c>
+      <c r="J186" s="5" t="n">
+        <v>1.145458</v>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>2.41073</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>23.226565</v>
+        <v>3.718306</v>
       </c>
       <c r="M186" s="5" t="n">
-        <v>23.908889</v>
+        <v>1.524189</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
@@ -23162,12 +23154,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Consulting fees - Pilot projects</t>
+          <t>Contractor fees (note 9)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -23201,18 +23193,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K187" s="5" t="n">
-        <v>0.372927</v>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>0.973942</v>
+      </c>
+      <c r="M187" s="5" t="n">
+        <v>1.563873</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
@@ -23248,17 +23238,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Revenue total</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -23281,28 +23271,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I188" s="5" t="n">
+        <v>0.01881</v>
+      </c>
+      <c r="J188" s="5" t="n">
+        <v>0.266545</v>
       </c>
       <c r="K188" s="5" t="n">
-        <v>0.372927</v>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.787968</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>1.408514</v>
+      </c>
+      <c r="M188" s="5" t="n">
+        <v>0.87295</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
@@ -23343,12 +23325,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Consulting fees (note 10)</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -23371,24 +23353,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I189" s="5" t="n">
+        <v>0.165683</v>
       </c>
       <c r="J189" s="5" t="n">
-        <v>0.301597</v>
+        <v>0.149271</v>
       </c>
       <c r="K189" s="5" t="n">
-        <v>0.477127</v>
+        <v>0.483479</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>0.973942</v>
-      </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.4847</v>
+      </c>
+      <c r="M189" s="5" t="n">
+        <v>0.359437</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
@@ -23429,7 +23407,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 7)</t>
+          <t>Bad debt expense</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -23459,13 +23437,15 @@
         </is>
       </c>
       <c r="J190" s="5" t="n">
-        <v>0.380386</v>
-      </c>
-      <c r="K190" s="5" t="n">
-        <v>1.472921</v>
+        <v>0.01725</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L190" s="5" t="n">
-        <v>2.791647</v>
+        <v>0.08648500000000001</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -23511,7 +23491,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (note 9) $</t>
+          <t>Stock-based compensation (note 6)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -23535,22 +23515,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I191" s="5" t="n">
-        <v>-5.3e-07</v>
-      </c>
-      <c r="J191" s="5" t="n">
-        <v>-1.2e-07</v>
-      </c>
-      <c r="K191" s="5" t="n">
-        <v>-3.1e-07</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L191" s="5" t="n">
-        <v>-4.5e-07</v>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.791647</v>
+      </c>
+      <c r="M191" s="5" t="n">
+        <v>0.9047190000000001</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
@@ -23586,15 +23570,19 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted (note 9)</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -23605,34 +23593,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G192" s="5" t="n">
+        <v>0.026939</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="I192" s="5" t="n">
+        <v>3.440042</v>
       </c>
       <c r="J192" s="5" t="n">
-        <v>15.518317</v>
+        <v>2.348152</v>
       </c>
       <c r="K192" s="5" t="n">
-        <v>18.820047</v>
+        <v>6.246497</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>23.226565</v>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.407594</v>
+      </c>
+      <c r="M192" s="5" t="n">
+        <v>5.358578</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
@@ -23668,15 +23648,19 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Consulting fees - Pilot projects $</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -23702,21 +23686,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J193" s="5" t="n">
-        <v>0.41067</v>
-      </c>
-      <c r="K193" s="5" t="n">
-        <v>0.372927</v>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>-10.407594</v>
+      </c>
+      <c r="M193" s="5" t="n">
+        <v>-5.358578</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
@@ -23752,12 +23736,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Consulting fees - Pilot projects (Note 4) $</t>
+          <t>Basic and diluted net loss per share (note 8) $</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -23786,23 +23770,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J194" s="5" t="n">
-        <v>0.41067</v>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L194" s="5" t="n">
+        <v>-4.5e-07</v>
+      </c>
+      <c r="M194" s="5" t="n">
+        <v>-2.2e-07</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
@@ -23838,19 +23820,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Consulting fees (note 11)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding, basic and diluted (note 8)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -23871,26 +23849,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I195" s="5" t="n">
-        <v>0.069565</v>
-      </c>
-      <c r="J195" s="5" t="n">
-        <v>0.301597</v>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L195" s="5" t="n">
+        <v>23.226565</v>
+      </c>
+      <c r="M195" s="5" t="n">
+        <v>23.908889</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -23926,12 +23904,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 8)</t>
+          <t>Consulting fees - Pilot projects</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -23955,16 +23933,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I196" s="5" t="n">
-        <v>0.015852</v>
-      </c>
-      <c r="J196" s="5" t="n">
-        <v>0.380386</v>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>0.372927</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -24010,15 +23990,19 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Listing expense (note 5)</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Revenue total</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -24039,18 +24023,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I197" s="5" t="n">
-        <v>2.853316</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K197" s="5" t="n">
+        <v>0.372927</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -24101,10 +24085,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (note 10) $</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>Consulting fees (note 10)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -24125,21 +24113,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I198" s="5" t="n">
-        <v>-5.3e-07</v>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J198" s="5" t="n">
-        <v>-1.2e-07</v>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.301597</v>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>0.477127</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>0.973942</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -24180,12 +24166,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted (note 10)</t>
+          <t>Stock-based compensation (note 7)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -24209,21 +24195,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I199" s="5" t="n">
-        <v>6.48019</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J199" s="5" t="n">
-        <v>15.518317</v>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.380386</v>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>1.472921</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>2.791647</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -24269,14 +24253,10 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Basic and diluted net loss per share (note 9) $</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -24298,22 +24278,16 @@
         </is>
       </c>
       <c r="I200" s="5" t="n">
-        <v>0.069565</v>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.3e-07</v>
+      </c>
+      <c r="J200" s="5" t="n">
+        <v>-1.2e-07</v>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>-3.1e-07</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>-4.5e-07</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -24354,12 +24328,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted (note 9)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -24383,23 +24357,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I201" s="5" t="n">
-        <v>0.015852</v>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" s="5" t="n">
+        <v>15.518317</v>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>18.820047</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>23.226565</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -24440,12 +24410,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted (note 9)</t>
+          <t>Consulting fees - Pilot projects $</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -24469,18 +24439,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I202" s="5" t="n">
-        <v>6.48019</v>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>0.372927</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -24526,12 +24494,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Professional fees (recovery) $</t>
+          <t>Consulting fees - Pilot projects (Note 4) $</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -24545,21 +24513,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G203" s="5" t="n">
-        <v>-0.003085</v>
-      </c>
-      <c r="H203" s="5" t="n">
-        <v>0.023272</v>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J203" s="5" t="n">
+        <v>0.41067</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -24615,10 +24585,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>Consulting fees (note 11)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -24629,21 +24603,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G204" s="5" t="n">
-        <v>0.030024</v>
-      </c>
-      <c r="H204" s="5" t="n">
-        <v>0.041969</v>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>0.069565</v>
+      </c>
+      <c r="J204" s="5" t="n">
+        <v>0.301597</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -24694,12 +24668,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Number     Amount      Surplus        Deficit        Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2012 2,031,300 $ 184,007 $ 7,213 $</t>
+          <t>Stock-based compensation (note 8)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -24713,21 +24687,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G205" s="5" t="n">
-        <v>0.00393</v>
-      </c>
-      <c r="H205" s="5" t="n">
-        <v>-0.18729</v>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>0.015852</v>
+      </c>
+      <c r="J205" s="5" t="n">
+        <v>0.380386</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -24778,12 +24752,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Number     Amount      Surplus        Deficit        Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - -</t>
+          <t>Listing expense (note 5)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -24797,16 +24771,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G206" s="5" t="n">
-        <v>-0.026939</v>
-      </c>
-      <c r="H206" s="5" t="n">
-        <v>-0.026939</v>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>2.853316</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -24862,12 +24838,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Number     Amount      Surplus        Deficit        Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2013 2,031,300 $ 184,007 $ 7,213 $</t>
+          <t>Basic and diluted net loss per share (note 10) $</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -24881,21 +24857,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G207" s="5" t="n">
-        <v>-0.023009</v>
-      </c>
-      <c r="H207" s="5" t="n">
-        <v>-0.214229</v>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>-5.3e-07</v>
+      </c>
+      <c r="J207" s="5" t="n">
+        <v>-1.2e-07</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -24946,12 +24922,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Number     Amount      Surplus        Deficit        Total</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Cancellation of seed common shares (note 1) (400,000) - -</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted (note 10)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -24975,15 +24951,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I208" s="5" t="n">
+        <v>6.48019</v>
+      </c>
+      <c r="J208" s="5" t="n">
+        <v>15.518317</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -25034,15 +25006,19 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Number     Amount      Surplus        Deficit        Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Private placement, net of costs (note 7(c)) 2,350,000 116,500 -</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -25053,18 +25029,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G209" s="5" t="n">
-        <v>0.1165</v>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I209" s="5" t="n">
+        <v>0.069565</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -25120,12 +25096,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Number     Amount      Surplus        Deficit        Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2014 3,981,300 $ 300,507 $ 7,213 $</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -25139,16 +25115,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G210" s="5" t="n">
-        <v>0.006491</v>
-      </c>
-      <c r="H210" s="5" t="n">
-        <v>-0.301229</v>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>0.015852</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -25204,17 +25182,19 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>March 28, 2011 to December</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted (note 9)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
-      <c r="E211" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25231,10 +25211,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I211" s="5" t="n">
+        <v>6.48019</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -25295,31 +25273,25 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="n">
-        <v>0.01838</v>
+          <t>Professional fees (recovery) $</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G212" s="5" t="n">
+        <v>-0.003085</v>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>0.023272</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -25385,31 +25357,25 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Other general and administrative</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E213" s="5" t="n">
-        <v>0.002722</v>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G213" s="5" t="n">
+        <v>0.030024</v>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>0.041969</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -25470,32 +25436,30 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number     Amount      Surplus        Deficit        Total</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Finances expenses</t>
+          <t>Balance, December 31, 2012 2,031,300 $ 184,007 $ 7,213 $</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" s="5" t="n">
-        <v>0.000393</v>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G214" s="5" t="n">
+        <v>0.00393</v>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>-0.18729</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -25556,36 +25520,30 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number     Amount      Surplus        Deficit        Total</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E215" s="5" t="n">
-        <v>-0.021495</v>
+          <t>Net loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G215" s="5" t="n">
+        <v>-0.026939</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>-0.026939</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -25646,32 +25604,30 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number     Amount      Surplus        Deficit        Total</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Comprehensive Loss per share 7 basic and fully $</t>
+          <t>Balance, December 31, 2013 2,031,300 $ 184,007 $ 7,213 $</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G216" s="5" t="n">
+        <v>-0.023009</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>-0.214229</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -25732,83 +25688,869 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
+          <t>Number     Amount      Surplus        Deficit        Total</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Cancellation of seed common shares (note 1) (400,000) - -</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Number     Amount      Surplus        Deficit        Total</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Private placement, net of costs (note 7(c)) 2,350,000 116,500 -</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Number     Amount      Surplus        Deficit        Total</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2014 3,981,300 $ 300,507 $ 7,213 $</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>0.006491</v>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>-0.301229</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>incorporation on</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>March 28, 2011 to December</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Other general and administrative</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>0.002722</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Finances expenses</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="5" t="n">
+        <v>0.000393</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="n">
+        <v>-0.021495</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Comprehensive Loss per share 7 basic and fully $</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
           <t>diluted)</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E217" s="5" t="n">
+      <c r="E226" s="5" t="n">
         <v>1.007273</v>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R217" t="inlineStr">
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
         <is>
           <t>-</t>
         </is>
